--- a/ig/xdsdocuments/ValueSet-MedComHCOTypeCodeVS.xlsx
+++ b/ig/xdsdocuments/ValueSet-MedComHCOTypeCodeVS.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="30">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-homecareobservation-draft</t>
+    <t>0.1.0-homecareobservation-draft-2</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T11:19:10+00:00</t>
+    <t>2026-04-30T11:35:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -93,19 +93,16 @@
     <t>BooleanType[null]</t>
   </si>
   <si>
-    <t>Concept</t>
-  </si>
-  <si>
-    <t>HCOM</t>
-  </si>
-  <si>
-    <t>HomeCareObservation message</t>
+    <t>Codes</t>
+  </si>
+  <si>
+    <t>All codes</t>
   </si>
   <si>
     <t>System URI</t>
   </si>
   <si>
-    <t>http://medcomfhir.dk/ig/xdsmetadata/ValueSet/MedCom-xds-typecode-VS</t>
+    <t>urn:oid:1.2.208.184.100.1</t>
   </si>
 </sst>
 </file>
@@ -378,17 +375,11 @@
       <c r="A1" t="s" s="1">
         <v>26</v>
       </c>
-      <c r="B1" t="s" s="1">
-        <v>20</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
         <v>27</v>
       </c>
-      <c r="B2" t="s" s="2">
-        <v>28</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
@@ -400,10 +391,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
+        <v>28</v>
+      </c>
+      <c r="B4" t="s" s="2">
         <v>29</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>30</v>
       </c>
     </row>
   </sheetData>
